--- a/events/Racice_2022_WC/Racice_2022_WC_Results.xlsx
+++ b/events/Racice_2022_WC/Racice_2022_WC_Results.xlsx
@@ -1532,6 +1532,11 @@
           <t>64580</t>
         </is>
       </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>61249</t>
+        </is>
+      </c>
       <c r="T15" t="inlineStr">
         <is>
           <t>118986</t>
@@ -2192,6 +2197,11 @@
           <t>+1.917</t>
         </is>
       </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>77386</t>
+        </is>
+      </c>
       <c r="S23" t="inlineStr">
         <is>
           <t>78723</t>
@@ -12752,6 +12762,11 @@
           <t>+0.820</t>
         </is>
       </c>
+      <c r="R164" t="inlineStr">
+        <is>
+          <t>42444</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -19250,6 +19265,11 @@
           <t>64580</t>
         </is>
       </c>
+      <c r="S258" t="inlineStr">
+        <is>
+          <t>61249</t>
+        </is>
+      </c>
       <c r="T258" t="inlineStr">
         <is>
           <t>118986</t>
@@ -19495,6 +19515,11 @@
           <t>+1.230</t>
         </is>
       </c>
+      <c r="R261" t="inlineStr">
+        <is>
+          <t>77386</t>
+        </is>
+      </c>
       <c r="S261" t="inlineStr">
         <is>
           <t>78723</t>
@@ -27425,6 +27450,11 @@
           <t>1:48.797</t>
         </is>
       </c>
+      <c r="R365" t="inlineStr">
+        <is>
+          <t>42444</t>
+        </is>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
@@ -34754,6 +34784,11 @@
           <t>42.264</t>
         </is>
       </c>
+      <c r="R471" t="inlineStr">
+        <is>
+          <t>42444</t>
+        </is>
+      </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
@@ -38603,6 +38638,11 @@
           <t>3:51.221</t>
         </is>
       </c>
+      <c r="R526" t="inlineStr">
+        <is>
+          <t>61249</t>
+        </is>
+      </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
@@ -40347,6 +40387,11 @@
           <t>+0.083</t>
         </is>
       </c>
+      <c r="R551" t="inlineStr">
+        <is>
+          <t>77386</t>
+        </is>
+      </c>
       <c r="S551" t="inlineStr">
         <is>
           <t>78723</t>
@@ -47169,6 +47214,11 @@
           <t>64580</t>
         </is>
       </c>
+      <c r="S642" t="inlineStr">
+        <is>
+          <t>61249</t>
+        </is>
+      </c>
       <c r="T642" t="inlineStr">
         <is>
           <t>118986</t>
@@ -50797,6 +50847,11 @@
           <t>+1.828</t>
         </is>
       </c>
+      <c r="R689" t="inlineStr">
+        <is>
+          <t>42444</t>
+        </is>
+      </c>
     </row>
     <row r="690">
       <c r="A690" t="inlineStr">
@@ -55555,6 +55610,11 @@
           <t>+0.013</t>
         </is>
       </c>
+      <c r="R756" t="inlineStr">
+        <is>
+          <t>77386</t>
+        </is>
+      </c>
       <c r="S756" t="inlineStr">
         <is>
           <t>78723</t>
@@ -70859,6 +70919,11 @@
           <t>+2.500</t>
         </is>
       </c>
+      <c r="R969" t="inlineStr">
+        <is>
+          <t>77386</t>
+        </is>
+      </c>
       <c r="S969" t="inlineStr">
         <is>
           <t>78723</t>
@@ -75079,6 +75144,11 @@
           <t>+0.430</t>
         </is>
       </c>
+      <c r="R1026" t="inlineStr">
+        <is>
+          <t>61249</t>
+        </is>
+      </c>
       <c r="S1026" t="inlineStr">
         <is>
           <t>118863</t>
@@ -82532,6 +82602,11 @@
           <t>39.727</t>
         </is>
       </c>
+      <c r="R1128" t="inlineStr">
+        <is>
+          <t>42444</t>
+        </is>
+      </c>
     </row>
     <row r="1129">
       <c r="A1129" t="inlineStr">
@@ -84480,6 +84555,11 @@
           <t>3:53.355</t>
         </is>
       </c>
+      <c r="R1155" t="inlineStr">
+        <is>
+          <t>61249</t>
+        </is>
+      </c>
     </row>
     <row r="1156">
       <c r="A1156" t="inlineStr">
@@ -86988,6 +87068,11 @@
           <t>+5.060</t>
         </is>
       </c>
+      <c r="R1189" t="inlineStr">
+        <is>
+          <t>77386</t>
+        </is>
+      </c>
       <c r="S1189" t="inlineStr">
         <is>
           <t>78723</t>
@@ -88573,6 +88658,11 @@
       <c r="Q1210" t="inlineStr">
         <is>
           <t>+1.040</t>
+        </is>
+      </c>
+      <c r="R1210" t="inlineStr">
+        <is>
+          <t>61249</t>
         </is>
       </c>
       <c r="S1210" t="inlineStr">
@@ -91944,7 +92034,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D493"/>
+  <dimension ref="A1:D496"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -102793,6 +102883,72 @@
         </is>
       </c>
     </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>61249</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>Alyssa</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>BULL</t>
+        </is>
+      </c>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>77386</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>Frederikke</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>MATTHIESEN</t>
+        </is>
+      </c>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>42444</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>Anja</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>OSTERMAN</t>
+        </is>
+      </c>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/events/Racice_2022_WC/Racice_2022_WC_Results.xlsx
+++ b/events/Racice_2022_WC/Racice_2022_WC_Results.xlsx
@@ -2627,6 +2627,11 @@
           <t>42426</t>
         </is>
       </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>42425</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2877,6 +2882,11 @@
           <t>65694</t>
         </is>
       </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>97652</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3362,6 +3372,11 @@
           <t>97611</t>
         </is>
       </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>97631</t>
+        </is>
+      </c>
       <c r="T37" t="inlineStr">
         <is>
           <t>88695</t>
@@ -4197,6 +4212,11 @@
           <t>118805</t>
         </is>
       </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>97726</t>
+        </is>
+      </c>
       <c r="U47" t="inlineStr">
         <is>
           <t>118804</t>
@@ -5537,6 +5557,11 @@
           <t>111737</t>
         </is>
       </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>97656</t>
+        </is>
+      </c>
       <c r="U63" t="inlineStr">
         <is>
           <t>111736</t>
@@ -8422,6 +8447,11 @@
           <t>+3.556</t>
         </is>
       </c>
+      <c r="R102" t="inlineStr">
+        <is>
+          <t>97902</t>
+        </is>
+      </c>
       <c r="S102" t="inlineStr">
         <is>
           <t>50167</t>
@@ -8797,6 +8827,11 @@
           <t>105031</t>
         </is>
       </c>
+      <c r="S107" t="inlineStr">
+        <is>
+          <t>97732</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -9692,6 +9727,11 @@
           <t>+5.453</t>
         </is>
       </c>
+      <c r="R120" t="inlineStr">
+        <is>
+          <t>97723</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -11752,6 +11792,11 @@
           <t>+4.074</t>
         </is>
       </c>
+      <c r="R150" t="inlineStr">
+        <is>
+          <t>42517</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -18100,6 +18145,11 @@
           <t>+11.678</t>
         </is>
       </c>
+      <c r="R242" t="inlineStr">
+        <is>
+          <t>97723</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -19310,6 +19360,11 @@
           <t>42426</t>
         </is>
       </c>
+      <c r="U259" t="inlineStr">
+        <is>
+          <t>42425</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -20395,6 +20450,11 @@
           <t>65694</t>
         </is>
       </c>
+      <c r="U272" t="inlineStr">
+        <is>
+          <t>97652</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -21730,6 +21790,11 @@
           <t>118805</t>
         </is>
       </c>
+      <c r="T289" t="inlineStr">
+        <is>
+          <t>97726</t>
+        </is>
+      </c>
       <c r="U289" t="inlineStr">
         <is>
           <t>118804</t>
@@ -23230,6 +23295,11 @@
           <t>97611</t>
         </is>
       </c>
+      <c r="S307" t="inlineStr">
+        <is>
+          <t>97631</t>
+        </is>
+      </c>
       <c r="T307" t="inlineStr">
         <is>
           <t>88695</t>
@@ -23400,6 +23470,11 @@
           <t>111737</t>
         </is>
       </c>
+      <c r="T309" t="inlineStr">
+        <is>
+          <t>97656</t>
+        </is>
+      </c>
       <c r="U309" t="inlineStr">
         <is>
           <t>111736</t>
@@ -23625,6 +23700,11 @@
           <t>+0.870</t>
         </is>
       </c>
+      <c r="R312" t="inlineStr">
+        <is>
+          <t>97902</t>
+        </is>
+      </c>
       <c r="S312" t="inlineStr">
         <is>
           <t>50167</t>
@@ -26540,6 +26620,11 @@
           <t>+6.860</t>
         </is>
       </c>
+      <c r="R353" t="inlineStr">
+        <is>
+          <t>97723</t>
+        </is>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -28405,6 +28490,11 @@
           <t>+4.707</t>
         </is>
       </c>
+      <c r="R380" t="inlineStr">
+        <is>
+          <t>42517</t>
+        </is>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
@@ -35783,6 +35873,11 @@
       <c r="L487" t="n">
         <v>2</v>
       </c>
+      <c r="R487" t="inlineStr">
+        <is>
+          <t>97732</t>
+        </is>
+      </c>
       <c r="X487" t="inlineStr">
         <is>
           <t>DSQ</t>
@@ -36468,6 +36563,11 @@
           <t>+3.310</t>
         </is>
       </c>
+      <c r="R497" t="inlineStr">
+        <is>
+          <t>97902</t>
+        </is>
+      </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
@@ -38168,6 +38268,11 @@
           <t>+0.413</t>
         </is>
       </c>
+      <c r="R521" t="inlineStr">
+        <is>
+          <t>97656</t>
+        </is>
+      </c>
       <c r="S521" t="inlineStr">
         <is>
           <t>77253</t>
@@ -39503,6 +39608,11 @@
           <t>+8.804</t>
         </is>
       </c>
+      <c r="R540" t="inlineStr">
+        <is>
+          <t>97652</t>
+        </is>
+      </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
@@ -39983,6 +40093,11 @@
           <t>+5.217</t>
         </is>
       </c>
+      <c r="R547" t="inlineStr">
+        <is>
+          <t>42517</t>
+        </is>
+      </c>
     </row>
     <row r="548">
       <c r="A548" t="inlineStr">
@@ -40809,6 +40924,11 @@
           <t>65694</t>
         </is>
       </c>
+      <c r="U557" t="inlineStr">
+        <is>
+          <t>97652</t>
+        </is>
+      </c>
     </row>
     <row r="558">
       <c r="A558" t="inlineStr">
@@ -41567,6 +41687,11 @@
           <t>118805</t>
         </is>
       </c>
+      <c r="T566" t="inlineStr">
+        <is>
+          <t>97726</t>
+        </is>
+      </c>
       <c r="U566" t="inlineStr">
         <is>
           <t>118804</t>
@@ -41644,6 +41769,11 @@
           <t>97611</t>
         </is>
       </c>
+      <c r="S567" t="inlineStr">
+        <is>
+          <t>97631</t>
+        </is>
+      </c>
       <c r="T567" t="inlineStr">
         <is>
           <t>88695</t>
@@ -43176,6 +43306,11 @@
           <t>+1.064</t>
         </is>
       </c>
+      <c r="R588" t="inlineStr">
+        <is>
+          <t>42517</t>
+        </is>
+      </c>
     </row>
     <row r="589">
       <c r="A589" t="inlineStr">
@@ -47263,6 +47398,11 @@
           <t>42426</t>
         </is>
       </c>
+      <c r="U644" t="inlineStr">
+        <is>
+          <t>42425</t>
+        </is>
+      </c>
     </row>
     <row r="645">
       <c r="A645" t="inlineStr">
@@ -49561,6 +49701,11 @@
           <t>+2.683</t>
         </is>
       </c>
+      <c r="R673" t="inlineStr">
+        <is>
+          <t>97902</t>
+        </is>
+      </c>
       <c r="S673" t="inlineStr">
         <is>
           <t>50167</t>
@@ -56869,6 +57014,11 @@
           <t>+1.733</t>
         </is>
       </c>
+      <c r="R775" t="inlineStr">
+        <is>
+          <t>42425</t>
+        </is>
+      </c>
       <c r="S775" t="inlineStr">
         <is>
           <t>39777</t>
@@ -58864,6 +59014,11 @@
           <t>+1.883</t>
         </is>
       </c>
+      <c r="R802" t="inlineStr">
+        <is>
+          <t>42724</t>
+        </is>
+      </c>
       <c r="S802" t="inlineStr">
         <is>
           <t>42728</t>
@@ -60344,6 +60499,11 @@
           <t>118805</t>
         </is>
       </c>
+      <c r="S822" t="inlineStr">
+        <is>
+          <t>97726</t>
+        </is>
+      </c>
     </row>
     <row r="823">
       <c r="A823" t="inlineStr">
@@ -64439,6 +64599,11 @@
           <t>+2.747</t>
         </is>
       </c>
+      <c r="R880" t="inlineStr">
+        <is>
+          <t>97902</t>
+        </is>
+      </c>
     </row>
     <row r="881">
       <c r="A881" t="inlineStr">
@@ -67099,6 +67264,11 @@
           <t>+9.324</t>
         </is>
       </c>
+      <c r="R918" t="inlineStr">
+        <is>
+          <t>42517</t>
+        </is>
+      </c>
     </row>
     <row r="919">
       <c r="A919" t="inlineStr">
@@ -67164,6 +67334,11 @@
           <t>+9.807</t>
         </is>
       </c>
+      <c r="R919" t="inlineStr">
+        <is>
+          <t>97652</t>
+        </is>
+      </c>
     </row>
     <row r="920">
       <c r="A920" t="inlineStr">
@@ -70224,6 +70399,11 @@
           <t>+3.507</t>
         </is>
       </c>
+      <c r="R962" t="inlineStr">
+        <is>
+          <t>42425</t>
+        </is>
+      </c>
       <c r="S962" t="inlineStr">
         <is>
           <t>39777</t>
@@ -73559,6 +73739,11 @@
           <t>+3.430</t>
         </is>
       </c>
+      <c r="R1007" t="inlineStr">
+        <is>
+          <t>97732</t>
+        </is>
+      </c>
       <c r="S1007" t="inlineStr">
         <is>
           <t>75588</t>
@@ -75404,6 +75589,11 @@
           <t>1:48.283</t>
         </is>
       </c>
+      <c r="R1032" t="inlineStr">
+        <is>
+          <t>97732</t>
+        </is>
+      </c>
       <c r="S1032" t="inlineStr">
         <is>
           <t>75588</t>
@@ -77797,6 +77987,11 @@
           <t>3:57.458</t>
         </is>
       </c>
+      <c r="R1065" t="inlineStr">
+        <is>
+          <t>97902</t>
+        </is>
+      </c>
     </row>
     <row r="1066">
       <c r="A1066" t="inlineStr">
@@ -79633,6 +79828,11 @@
           <t>1:44.486</t>
         </is>
       </c>
+      <c r="R1091" t="inlineStr">
+        <is>
+          <t>42425</t>
+        </is>
+      </c>
       <c r="S1091" t="inlineStr">
         <is>
           <t>39777</t>
@@ -83909,6 +84109,11 @@
           <t>+3.104</t>
         </is>
       </c>
+      <c r="R1149" t="inlineStr">
+        <is>
+          <t>97656</t>
+        </is>
+      </c>
       <c r="S1149" t="inlineStr">
         <is>
           <t>77253</t>
@@ -88075,6 +88280,11 @@
           <t>+5.833</t>
         </is>
       </c>
+      <c r="R1205" t="inlineStr">
+        <is>
+          <t>97732</t>
+        </is>
+      </c>
       <c r="S1205" t="inlineStr">
         <is>
           <t>75588</t>
@@ -90310,6 +90520,11 @@
           <t>+1:46.645</t>
         </is>
       </c>
+      <c r="R1236" t="inlineStr">
+        <is>
+          <t>97902</t>
+        </is>
+      </c>
     </row>
     <row r="1237">
       <c r="A1237" t="inlineStr">
@@ -93570,6 +93785,11 @@
           <t>+1:15.026</t>
         </is>
       </c>
+      <c r="R1284" t="inlineStr">
+        <is>
+          <t>42724</t>
+        </is>
+      </c>
     </row>
     <row r="1285">
       <c r="A1285" t="inlineStr">
@@ -94470,6 +94690,11 @@
       </c>
       <c r="N1297" t="n">
         <v>27</v>
+      </c>
+      <c r="R1297" t="inlineStr">
+        <is>
+          <t>97723</t>
+        </is>
       </c>
     </row>
     <row r="1298">
@@ -94912,7 +95137,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D490"/>
+  <dimension ref="A1:D500"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -105695,6 +105920,226 @@
         </is>
       </c>
     </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>42425</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>Agata</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>FANTINI</t>
+        </is>
+      </c>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>97652</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>Anna</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>HANSEN</t>
+        </is>
+      </c>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>97631</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>Mark</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>SZENDY</t>
+        </is>
+      </c>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>97726</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>Taehyeon</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>KIM</t>
+        </is>
+      </c>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>97656</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>Philip</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>BRYDE</t>
+        </is>
+      </c>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>97902</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>Gabriele</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>CASADEI</t>
+        </is>
+      </c>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>97732</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>Mihai</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>CHIHAIA</t>
+        </is>
+      </c>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>97723</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>Gihong</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>GWON</t>
+        </is>
+      </c>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>42517</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>Esti</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>OLIVIER</t>
+        </is>
+      </c>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>42724</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>Daniel</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>DAL BO</t>
+        </is>
+      </c>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/events/Racice_2022_WC/Racice_2022_WC_Results.xlsx
+++ b/events/Racice_2022_WC/Racice_2022_WC_Results.xlsx
@@ -1457,6 +1457,11 @@
           <t>118638</t>
         </is>
       </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>84885</t>
+        </is>
+      </c>
       <c r="U14" t="inlineStr">
         <is>
           <t>118635</t>
@@ -1947,6 +1952,11 @@
           <t>1:34.523</t>
         </is>
       </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>85124</t>
+        </is>
+      </c>
       <c r="S20" t="inlineStr">
         <is>
           <t>70317</t>
@@ -3872,6 +3882,11 @@
           <t>36449</t>
         </is>
       </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>36453</t>
+        </is>
+      </c>
       <c r="T43" t="inlineStr">
         <is>
           <t>72841</t>
@@ -5717,6 +5732,11 @@
           <t>+16.461</t>
         </is>
       </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>42587</t>
+        </is>
+      </c>
       <c r="S65" t="inlineStr">
         <is>
           <t>102697</t>
@@ -5867,6 +5887,11 @@
           <t>+2.986</t>
         </is>
       </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>95617</t>
+        </is>
+      </c>
       <c r="S67" t="inlineStr">
         <is>
           <t>100406</t>
@@ -7197,6 +7222,11 @@
           <t>+3.867</t>
         </is>
       </c>
+      <c r="R85" t="inlineStr">
+        <is>
+          <t>46387</t>
+        </is>
+      </c>
       <c r="S85" t="inlineStr">
         <is>
           <t>46394</t>
@@ -7492,6 +7522,11 @@
           <t>+4.707</t>
         </is>
       </c>
+      <c r="R89" t="inlineStr">
+        <is>
+          <t>79493</t>
+        </is>
+      </c>
       <c r="S89" t="inlineStr">
         <is>
           <t>118994</t>
@@ -8232,6 +8267,11 @@
           <t>98917</t>
         </is>
       </c>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>97941</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -18215,6 +18255,11 @@
           <t>+33.816</t>
         </is>
       </c>
+      <c r="R243" t="inlineStr">
+        <is>
+          <t>42587</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -19940,6 +19985,11 @@
           <t>118638</t>
         </is>
       </c>
+      <c r="T266" t="inlineStr">
+        <is>
+          <t>84885</t>
+        </is>
+      </c>
       <c r="U266" t="inlineStr">
         <is>
           <t>118635</t>
@@ -23130,6 +23180,11 @@
           <t>36449</t>
         </is>
       </c>
+      <c r="S305" t="inlineStr">
+        <is>
+          <t>36453</t>
+        </is>
+      </c>
       <c r="T305" t="inlineStr">
         <is>
           <t>72841</t>
@@ -24150,6 +24205,11 @@
           <t>+3.707</t>
         </is>
       </c>
+      <c r="R318" t="inlineStr">
+        <is>
+          <t>46387</t>
+        </is>
+      </c>
       <c r="S318" t="inlineStr">
         <is>
           <t>46394</t>
@@ -24515,6 +24575,11 @@
           <t>+2.094</t>
         </is>
       </c>
+      <c r="R323" t="inlineStr">
+        <is>
+          <t>79493</t>
+        </is>
+      </c>
       <c r="S323" t="inlineStr">
         <is>
           <t>118994</t>
@@ -31804,6 +31869,11 @@
           <t>45.264</t>
         </is>
       </c>
+      <c r="R428" t="inlineStr">
+        <is>
+          <t>95617</t>
+        </is>
+      </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
@@ -35614,6 +35684,11 @@
           <t>+4.500</t>
         </is>
       </c>
+      <c r="R483" t="inlineStr">
+        <is>
+          <t>79493</t>
+        </is>
+      </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
@@ -41165,6 +41240,11 @@
           <t>36449</t>
         </is>
       </c>
+      <c r="S560" t="inlineStr">
+        <is>
+          <t>36453</t>
+        </is>
+      </c>
       <c r="T560" t="inlineStr">
         <is>
           <t>72841</t>
@@ -42000,6 +42080,11 @@
           <t>+0.643</t>
         </is>
       </c>
+      <c r="R570" t="inlineStr">
+        <is>
+          <t>46387</t>
+        </is>
+      </c>
       <c r="S570" t="inlineStr">
         <is>
           <t>46394</t>
@@ -42380,6 +42465,11 @@
           <t>+3.643</t>
         </is>
       </c>
+      <c r="R575" t="inlineStr">
+        <is>
+          <t>79493</t>
+        </is>
+      </c>
       <c r="S575" t="inlineStr">
         <is>
           <t>118994</t>
@@ -47055,6 +47145,11 @@
           <t>118638</t>
         </is>
       </c>
+      <c r="T640" t="inlineStr">
+        <is>
+          <t>84885</t>
+        </is>
+      </c>
       <c r="U640" t="inlineStr">
         <is>
           <t>118635</t>
@@ -47127,6 +47222,11 @@
           <t>+1.153</t>
         </is>
       </c>
+      <c r="R641" t="inlineStr">
+        <is>
+          <t>85124</t>
+        </is>
+      </c>
       <c r="S641" t="inlineStr">
         <is>
           <t>70317</t>
@@ -47716,6 +47816,11 @@
           <t>+3.667</t>
         </is>
       </c>
+      <c r="R648" t="inlineStr">
+        <is>
+          <t>95617</t>
+        </is>
+      </c>
       <c r="S648" t="inlineStr">
         <is>
           <t>100406</t>
@@ -49095,6 +49200,11 @@
           <t>98917</t>
         </is>
       </c>
+      <c r="S665" t="inlineStr">
+        <is>
+          <t>97941</t>
+        </is>
+      </c>
     </row>
     <row r="666">
       <c r="A666" t="inlineStr">
@@ -49773,6 +49883,11 @@
           <t>42.061</t>
         </is>
       </c>
+      <c r="R674" t="inlineStr">
+        <is>
+          <t>95617</t>
+        </is>
+      </c>
       <c r="S674" t="inlineStr">
         <is>
           <t>100406</t>
@@ -52200,6 +52315,11 @@
           <t>+5.107</t>
         </is>
       </c>
+      <c r="R708" t="inlineStr">
+        <is>
+          <t>118700</t>
+        </is>
+      </c>
     </row>
     <row r="709">
       <c r="A709" t="inlineStr">
@@ -58049,6 +58169,11 @@
           <t>+0.037</t>
         </is>
       </c>
+      <c r="R789" t="inlineStr">
+        <is>
+          <t>36453</t>
+        </is>
+      </c>
       <c r="S789" t="inlineStr">
         <is>
           <t>72841</t>
@@ -59904,6 +60029,11 @@
           <t>+26.005</t>
         </is>
       </c>
+      <c r="R814" t="inlineStr">
+        <is>
+          <t>42587</t>
+        </is>
+      </c>
       <c r="S814" t="inlineStr">
         <is>
           <t>102696</t>
@@ -64464,6 +64594,11 @@
           <t>+0.600</t>
         </is>
       </c>
+      <c r="R878" t="inlineStr">
+        <is>
+          <t>79493</t>
+        </is>
+      </c>
     </row>
     <row r="879">
       <c r="A879" t="inlineStr">
@@ -73004,6 +73139,11 @@
           <t>+0.247</t>
         </is>
       </c>
+      <c r="R997" t="inlineStr">
+        <is>
+          <t>36453</t>
+        </is>
+      </c>
       <c r="S997" t="inlineStr">
         <is>
           <t>72841</t>
@@ -81964,6 +82104,11 @@
           <t>45.086</t>
         </is>
       </c>
+      <c r="R1119" t="inlineStr">
+        <is>
+          <t>95617</t>
+        </is>
+      </c>
     </row>
     <row r="1120">
       <c r="A1120" t="inlineStr">
@@ -83672,6 +83817,11 @@
           <t>+4.625</t>
         </is>
       </c>
+      <c r="R1143" t="inlineStr">
+        <is>
+          <t>79493</t>
+        </is>
+      </c>
     </row>
     <row r="1144">
       <c r="A1144" t="inlineStr">
@@ -87371,6 +87521,11 @@
           <t>+0.548</t>
         </is>
       </c>
+      <c r="R1193" t="inlineStr">
+        <is>
+          <t>36453</t>
+        </is>
+      </c>
       <c r="S1193" t="inlineStr">
         <is>
           <t>72841</t>
@@ -89271,6 +89426,11 @@
           <t>25:06.687</t>
         </is>
       </c>
+      <c r="R1218" t="inlineStr">
+        <is>
+          <t>118700</t>
+        </is>
+      </c>
     </row>
     <row r="1219">
       <c r="A1219" t="inlineStr">
@@ -90093,6 +90253,11 @@
           <t>+28.046</t>
         </is>
       </c>
+      <c r="R1230" t="inlineStr">
+        <is>
+          <t>79493</t>
+        </is>
+      </c>
     </row>
     <row r="1231">
       <c r="A1231" t="inlineStr">
@@ -91748,6 +91913,11 @@
       <c r="Q1254" t="inlineStr">
         <is>
           <t>+27.151</t>
+        </is>
+      </c>
+      <c r="R1254" t="inlineStr">
+        <is>
+          <t>84885</t>
         </is>
       </c>
     </row>
@@ -95137,7 +95307,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D500"/>
+  <dimension ref="A1:D509"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -106140,6 +106310,204 @@
         </is>
       </c>
     </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>36453</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>Joao</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>RIBEIRO</t>
+        </is>
+      </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>42587</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>Tsz Chun</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>CHEUNG</t>
+        </is>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>46387</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>Vitaliy</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>VERHELES</t>
+        </is>
+      </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>79493</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>Jose Ramon</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>PELIER CORDOVA</t>
+        </is>
+      </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>84885</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>Luan</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>YANG</t>
+        </is>
+      </c>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>85124</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>Lena</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>ROEHLINGS</t>
+        </is>
+      </c>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>95617</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>Yarisleidis</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>CIRILO DUBOY</t>
+        </is>
+      </c>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>97941</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>Pablo</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>MARTINEZ</t>
+        </is>
+      </c>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>118700</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>Li</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/events/Racice_2022_WC/Racice_2022_WC_Results.xlsx
+++ b/events/Racice_2022_WC/Racice_2022_WC_Results.xlsx
@@ -11352,6 +11352,11 @@
           <t>+3.987</t>
         </is>
       </c>
+      <c r="R143" t="inlineStr">
+        <is>
+          <t>47779</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -27935,6 +27940,11 @@
           <t>+7.097</t>
         </is>
       </c>
+      <c r="R371" t="inlineStr">
+        <is>
+          <t>47779</t>
+        </is>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
@@ -34994,6 +35004,11 @@
           <t>+1.820</t>
         </is>
       </c>
+      <c r="R473" t="inlineStr">
+        <is>
+          <t>47779</t>
+        </is>
+      </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
@@ -39408,6 +39423,11 @@
           <t>+5.627</t>
         </is>
       </c>
+      <c r="R536" t="inlineStr">
+        <is>
+          <t>47779</t>
+        </is>
+      </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
@@ -43329,6 +43349,11 @@
           <t>+0.387</t>
         </is>
       </c>
+      <c r="R587" t="inlineStr">
+        <is>
+          <t>47779</t>
+        </is>
+      </c>
     </row>
     <row r="588">
       <c r="A588" t="inlineStr">
@@ -63769,6 +63794,11 @@
           <t>+2.614</t>
         </is>
       </c>
+      <c r="R866" t="inlineStr">
+        <is>
+          <t>47779</t>
+        </is>
+      </c>
     </row>
     <row r="867">
       <c r="A867" t="inlineStr">
@@ -67124,6 +67154,11 @@
           <t>+1.787</t>
         </is>
       </c>
+      <c r="R914" t="inlineStr">
+        <is>
+          <t>47779</t>
+        </is>
+      </c>
     </row>
     <row r="915">
       <c r="A915" t="inlineStr">
@@ -77705,6 +77740,11 @@
           <t>+0.720</t>
         </is>
       </c>
+      <c r="R1059" t="inlineStr">
+        <is>
+          <t>47779</t>
+        </is>
+      </c>
     </row>
     <row r="1060">
       <c r="A1060" t="inlineStr">
@@ -78912,6 +78952,11 @@
       <c r="Q1076" t="inlineStr">
         <is>
           <t>+1.867</t>
+        </is>
+      </c>
+      <c r="R1076" t="inlineStr">
+        <is>
+          <t>47779</t>
         </is>
       </c>
     </row>
@@ -95307,7 +95352,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D509"/>
+  <dimension ref="A1:D510"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -106508,6 +106553,28 @@
         </is>
       </c>
     </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>47779</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>Kristina</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>BEDEC</t>
+        </is>
+      </c>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
